--- a/5-2026.xlsx
+++ b/5-2026.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\python\balanceSheet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC45B258-BA4B-4CA8-AF66-A884944263BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F503A8CD-C70D-4849-8D87-686A8909DD4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="12480" xr2:uid="{22711B75-76D9-4178-BA38-3EFE03212E7F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C7DBF94B-76D0-4DB1-B5F9-1612F1925133}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AB$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$24</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -114,11 +114,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="m\-yyyy"/>
-    <numFmt numFmtId="166" formatCode="B1mmm\-yy"/>
+    <numFmt numFmtId="164" formatCode="m\-yyyy"/>
+    <numFmt numFmtId="165" formatCode="B1mmm\-yy"/>
     <numFmt numFmtId="167" formatCode="_-* #,##0\ _ج_._م_._‏_-;\-* #,##0\ _ج_._م_._‏_-;_-* &quot;-&quot;\ _ج_._م_._‏_-;_-@_-"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -182,14 +182,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <u/>
       <sz val="14"/>
       <name val="Arial"/>
@@ -205,7 +197,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -215,12 +207,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -287,24 +273,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -313,58 +287,37 @@
     <xf numFmtId="43" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="4" fontId="6" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="43" fontId="6" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="6" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="6" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="7" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="7" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="9" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="7" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -681,719 +634,712 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2387683F-6A26-4967-9F2B-AE7C8F037119}">
-  <dimension ref="A1:J27"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4E14BED-4A82-49F0-AB48-4A735E1CAC39}">
+  <dimension ref="A1:I24"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.5" style="4" customWidth="1"/>
-    <col min="2" max="3" width="20.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="15.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="34.09765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="19.69921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="14.8984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="5" customFormat="1" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="6">
+    <row r="1" spans="1:9" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2">
+        <v>46235</v>
+      </c>
+      <c r="C1" s="2">
         <v>46204</v>
       </c>
-      <c r="C1" s="6">
+      <c r="D1" s="2">
         <v>46174</v>
       </c>
-      <c r="D1" s="6">
+      <c r="E1" s="2">
         <v>46143</v>
       </c>
-      <c r="E1" s="6">
+      <c r="F1" s="2">
         <v>46113</v>
       </c>
-      <c r="F1" s="6">
+      <c r="G1" s="2">
         <v>46082</v>
       </c>
-      <c r="G1" s="6">
+      <c r="H1" s="2">
         <v>46054</v>
       </c>
-      <c r="H1" s="6">
+      <c r="I1" s="2">
         <v>46023</v>
       </c>
-      <c r="I1" s="6">
-        <v>45992</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="7" t="s">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="4">
+        <v>29603786.460000001</v>
+      </c>
+      <c r="C2" s="4">
         <v>23560668.130000003</v>
       </c>
-      <c r="C2" s="8">
+      <c r="D2" s="4">
         <v>22199177.149999999</v>
       </c>
-      <c r="D2" s="8">
+      <c r="E2" s="4">
         <v>21766987.909999996</v>
       </c>
-      <c r="E2" s="8">
+      <c r="F2" s="4">
         <v>21958105.329999998</v>
       </c>
-      <c r="F2" s="10">
+      <c r="G2" s="5">
         <v>19733077.309999999</v>
       </c>
-      <c r="G2" s="10">
+      <c r="H2" s="5">
         <v>19903916.759999998</v>
       </c>
-      <c r="H2" s="10">
+      <c r="I2" s="5">
         <v>20074784.07</v>
       </c>
-      <c r="I2" s="11">
-        <v>20245724.849999998</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="7" t="s">
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="6">
+        <v>2394454.15</v>
+      </c>
+      <c r="C3" s="6">
         <v>2373214.15</v>
       </c>
-      <c r="C3" s="12">
+      <c r="D3" s="6">
         <v>2373214.15</v>
       </c>
-      <c r="D3" s="12">
+      <c r="E3" s="6">
         <v>2357614.15</v>
       </c>
-      <c r="E3" s="12">
+      <c r="F3" s="6">
         <v>2346114.15</v>
       </c>
-      <c r="F3" s="13">
+      <c r="G3" s="7">
         <v>2232984.15</v>
       </c>
-      <c r="G3" s="13">
+      <c r="H3" s="7">
         <v>2200362.15</v>
       </c>
-      <c r="H3" s="13">
+      <c r="I3" s="7">
         <v>1884602.5</v>
       </c>
-      <c r="I3" s="14">
-        <v>1884602.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="7" t="s">
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="6">
         <v>596741</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="6">
         <v>596741</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="6">
         <v>596741</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="6">
         <v>596741</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="6">
         <v>596741</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="7">
         <v>596741</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="7">
         <v>596741</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="7">
         <v>596741</v>
       </c>
     </row>
-    <row r="5" spans="1:9" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+    <row r="5" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="16">
+      <c r="B5" s="9">
+        <v>32594981.609999999</v>
+      </c>
+      <c r="C5" s="9">
         <v>26530623.280000001</v>
       </c>
-      <c r="C5" s="16">
+      <c r="D5" s="9">
         <v>25169132.299999997</v>
       </c>
-      <c r="D5" s="16">
+      <c r="E5" s="9">
         <v>24721343.059999995</v>
       </c>
-      <c r="E5" s="16">
+      <c r="F5" s="9">
         <v>24900960.479999997</v>
       </c>
-      <c r="F5" s="17">
+      <c r="G5" s="10">
         <v>22562802.459999997</v>
       </c>
-      <c r="G5" s="17">
+      <c r="H5" s="10">
         <v>22701019.909999996</v>
       </c>
-      <c r="H5" s="17">
+      <c r="I5" s="10">
         <v>22556127.57</v>
       </c>
-      <c r="I5" s="17">
-        <v>22727068.349999998</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="7" t="s">
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="6">
+        <v>317508844.450001</v>
+      </c>
+      <c r="C6" s="6">
         <v>309138879.46999943</v>
       </c>
-      <c r="C6" s="12">
+      <c r="D6" s="6">
         <v>309527001.88999999</v>
       </c>
-      <c r="D6" s="12">
+      <c r="E6" s="6">
         <v>307962482.93999964</v>
       </c>
-      <c r="E6" s="12">
+      <c r="F6" s="6">
         <v>251497026.58999923</v>
       </c>
-      <c r="F6" s="13">
+      <c r="G6" s="7">
         <v>216736145.83000055</v>
       </c>
-      <c r="G6" s="13">
+      <c r="H6" s="7">
         <v>246421191.35999998</v>
       </c>
-      <c r="H6" s="13">
+      <c r="I6" s="7">
         <v>276755395.22999948</v>
       </c>
-      <c r="I6" s="14">
-        <v>263703635.98999962</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="12">
-        <v>70184274.540000036</v>
-      </c>
-      <c r="C7" s="12">
-        <v>59455323.910000071</v>
-      </c>
-      <c r="D7" s="12">
-        <v>53625668.39000012</v>
-      </c>
-      <c r="E7" s="12">
-        <v>35200506.069999754</v>
-      </c>
-      <c r="F7" s="13">
+      <c r="B7" s="6">
+        <v>151212713.38999975</v>
+      </c>
+      <c r="C7" s="6">
+        <v>67911151.629999876</v>
+      </c>
+      <c r="D7" s="6">
+        <v>57255422.389999941</v>
+      </c>
+      <c r="E7" s="6">
+        <v>51419810.890000179</v>
+      </c>
+      <c r="F7" s="6">
+        <v>34279393.569999754</v>
+      </c>
+      <c r="G7" s="7">
         <v>36391015.480000034</v>
       </c>
-      <c r="G7" s="13">
+      <c r="H7" s="7">
         <v>35044469.309999794</v>
       </c>
-      <c r="H7" s="13">
+      <c r="I7" s="7">
         <v>40312392.319999546</v>
       </c>
-      <c r="I7" s="14">
-        <v>35899338.66000022</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="12">
-        <v>51209264.369999841</v>
-      </c>
-      <c r="C8" s="12">
-        <v>59369229.920000523</v>
-      </c>
-      <c r="D8" s="12">
+      <c r="B8" s="6">
+        <v>61358688.860000148</v>
+      </c>
+      <c r="C8" s="6">
+        <v>51205838.399999842</v>
+      </c>
+      <c r="D8" s="6">
+        <v>59365803.950000517</v>
+      </c>
+      <c r="E8" s="6">
         <v>88773553.039999709</v>
       </c>
-      <c r="E8" s="12">
+      <c r="F8" s="6">
         <v>80049672.870000184</v>
       </c>
-      <c r="F8" s="13">
+      <c r="G8" s="7">
         <v>69103414.059999168</v>
       </c>
-      <c r="G8" s="13">
+      <c r="H8" s="7">
         <v>62152170.890000343</v>
       </c>
-      <c r="H8" s="13">
+      <c r="I8" s="7">
         <v>73211384.189999923</v>
       </c>
-      <c r="I8" s="14">
-        <v>55796550.240000226</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="12">
-        <v>172600094.34999996</v>
-      </c>
-      <c r="C9" s="12">
+      <c r="B9" s="6">
+        <v>263356694.12</v>
+      </c>
+      <c r="C9" s="6">
+        <v>172668288.80999997</v>
+      </c>
+      <c r="D9" s="6">
         <v>149690756.01999947</v>
       </c>
-      <c r="D9" s="12">
+      <c r="E9" s="6">
         <v>144670090.74999979</v>
       </c>
-      <c r="E9" s="12">
+      <c r="F9" s="6">
         <v>122145542.94999963</v>
       </c>
-      <c r="F9" s="13">
+      <c r="G9" s="7">
         <v>111928881.3599996</v>
       </c>
-      <c r="G9" s="13">
+      <c r="H9" s="7">
         <v>109562688.63999996</v>
       </c>
-      <c r="H9" s="13">
+      <c r="I9" s="7">
         <v>125746266.17999986</v>
       </c>
-      <c r="I9" s="14">
-        <v>137039113.50999942</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="7" t="s">
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="6">
+        <v>21478836.109999999</v>
+      </c>
+      <c r="C10" s="6">
         <v>21646985.150000002</v>
       </c>
-      <c r="C10" s="12">
+      <c r="D10" s="6">
         <v>3637923.2</v>
       </c>
-      <c r="D10" s="12">
+      <c r="E10" s="6">
         <v>3416615.87</v>
       </c>
-      <c r="E10" s="12">
+      <c r="F10" s="6">
         <v>3637923.2</v>
       </c>
-      <c r="F10" s="13">
+      <c r="G10" s="7">
         <v>3637923.2</v>
       </c>
-      <c r="G10" s="13">
+      <c r="H10" s="7">
         <v>3404110.7</v>
       </c>
-      <c r="H10" s="13">
+      <c r="I10" s="7">
         <v>3636923.24</v>
       </c>
-      <c r="I10" s="14">
-        <v>4006885.54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
+    </row>
+    <row r="11" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="16">
-        <v>624779497.87999928</v>
-      </c>
-      <c r="C11" s="16">
-        <v>581680234.94000018</v>
-      </c>
-      <c r="D11" s="16">
-        <v>598448410.98999929</v>
-      </c>
-      <c r="E11" s="16">
-        <v>492530671.67999882</v>
-      </c>
-      <c r="F11" s="17">
+      <c r="B11" s="9">
+        <v>814915776.9300009</v>
+      </c>
+      <c r="C11" s="9">
+        <v>622571143.45999908</v>
+      </c>
+      <c r="D11" s="9">
+        <v>579476907.44999993</v>
+      </c>
+      <c r="E11" s="9">
+        <v>596242553.48999929</v>
+      </c>
+      <c r="F11" s="9">
+        <v>491609559.17999882</v>
+      </c>
+      <c r="G11" s="10">
         <v>437797379.92999935</v>
       </c>
-      <c r="G11" s="17">
+      <c r="H11" s="10">
         <v>456584630.90000004</v>
       </c>
-      <c r="H11" s="17">
+      <c r="I11" s="10">
         <v>519662361.15999877</v>
       </c>
-      <c r="I11" s="17">
-        <v>496445523.93999952</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" s="20" customFormat="1" ht="18" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
+    </row>
+    <row r="12" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A12" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="21">
-        <v>651310121.15999925</v>
-      </c>
-      <c r="C12" s="21">
-        <v>606849367.24000013</v>
-      </c>
-      <c r="D12" s="21">
-        <v>623169754.04999924</v>
-      </c>
-      <c r="E12" s="22">
-        <v>517431632.15999883</v>
-      </c>
-      <c r="F12" s="22">
+      <c r="B12" s="15">
+        <v>847510758.54000092</v>
+      </c>
+      <c r="C12" s="15">
+        <v>649101766.73999906</v>
+      </c>
+      <c r="D12" s="15">
+        <v>604646039.74999988</v>
+      </c>
+      <c r="E12" s="15">
+        <v>620963896.54999924</v>
+      </c>
+      <c r="F12" s="12">
+        <v>516510519.65999883</v>
+      </c>
+      <c r="G12" s="12">
         <v>460360182.38999933</v>
       </c>
-      <c r="G12" s="22">
+      <c r="H12" s="12">
         <v>479285650.81000006</v>
       </c>
-      <c r="H12" s="22">
+      <c r="I12" s="12">
         <v>542218488.72999883</v>
       </c>
-      <c r="I12" s="22">
-        <v>519172592.28999954</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="7" t="s">
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="6">
+        <v>390277405.91999996</v>
+      </c>
+      <c r="C13" s="6">
         <v>253155600.78000042</v>
       </c>
-      <c r="C13" s="12">
+      <c r="D13" s="6">
         <v>216556629.12999955</v>
       </c>
-      <c r="D13" s="12">
+      <c r="E13" s="6">
         <v>221490803.47</v>
       </c>
-      <c r="E13" s="12">
+      <c r="F13" s="6">
         <v>120354247.44999973</v>
       </c>
-      <c r="F13" s="13">
+      <c r="G13" s="7">
         <v>105458756.66999979</v>
       </c>
-      <c r="G13" s="13">
+      <c r="H13" s="7">
         <v>133665877.53000003</v>
       </c>
-      <c r="H13" s="13">
+      <c r="I13" s="7">
         <v>177227503.53999999</v>
       </c>
-      <c r="I13" s="14">
-        <v>148043033.26000029</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="7" t="s">
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="12">
-        <v>15250449.870000014</v>
-      </c>
-      <c r="C14" s="12">
-        <v>12386398.509999959</v>
-      </c>
-      <c r="D14" s="12">
+      <c r="B14" s="6">
+        <v>14045413.12999998</v>
+      </c>
+      <c r="C14" s="6">
+        <v>15241394.300000006</v>
+      </c>
+      <c r="D14" s="6">
+        <v>12216539.409999972</v>
+      </c>
+      <c r="E14" s="6">
         <v>17960661.13000001</v>
       </c>
-      <c r="E14" s="12">
+      <c r="F14" s="6">
         <v>24891599.720000021</v>
       </c>
-      <c r="F14" s="13">
+      <c r="G14" s="7">
         <v>21895473.599999938</v>
       </c>
-      <c r="G14" s="13">
+      <c r="H14" s="7">
         <v>24608773.970000006</v>
       </c>
-      <c r="H14" s="13">
+      <c r="I14" s="7">
         <v>28574676.589999989</v>
       </c>
-      <c r="I14" s="14">
-        <v>26189842.269999973</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="7" t="s">
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="6">
+        <v>154629693.79000002</v>
+      </c>
+      <c r="C15" s="6">
         <v>101654934.77000012</v>
       </c>
-      <c r="C15" s="12">
+      <c r="D15" s="6">
         <v>96198307.679999903</v>
       </c>
-      <c r="D15" s="12">
+      <c r="E15" s="6">
         <v>104414415.23000011</v>
       </c>
-      <c r="E15" s="12">
+      <c r="F15" s="6">
         <v>102984255.44000015</v>
       </c>
-      <c r="F15" s="13">
+      <c r="G15" s="7">
         <v>77233877.720000073</v>
       </c>
-      <c r="G15" s="13">
+      <c r="H15" s="7">
         <v>72327612.63000001</v>
       </c>
-      <c r="H15" s="13">
+      <c r="I15" s="7">
         <v>93766086.059999973</v>
       </c>
-      <c r="I15" s="14">
-        <v>107449108.75</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="7" t="s">
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="7">
         <v>786966</v>
       </c>
-      <c r="C16" s="13">
+      <c r="C16" s="7">
         <v>786966</v>
       </c>
-      <c r="D16" s="13">
+      <c r="D16" s="7">
         <v>786966</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="7">
         <v>786966</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="7">
         <v>786966</v>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="7">
         <v>786966</v>
       </c>
-      <c r="H16" s="13">
+      <c r="H16" s="7">
         <v>786966</v>
       </c>
-      <c r="I16" s="14">
+      <c r="I16" s="7">
         <v>786966</v>
       </c>
     </row>
-    <row r="17" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="7" t="s">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="12">
-        <v>517682.89999872731</v>
-      </c>
-      <c r="C17" s="12">
-        <v>517679.67000000045</v>
-      </c>
-      <c r="D17" s="12">
+      <c r="B17" s="6">
+        <v>517679.65999836015</v>
+      </c>
+      <c r="C17" s="6">
+        <v>517679.65999836015</v>
+      </c>
+      <c r="D17" s="6">
+        <v>517679.96000033902</v>
+      </c>
+      <c r="E17" s="6">
         <v>517679.73999911832</v>
       </c>
-      <c r="E17" s="12">
+      <c r="F17" s="6">
         <v>517679.65999889659</v>
       </c>
-      <c r="F17" s="13">
+      <c r="G17" s="7">
         <v>517679.64999807166</v>
       </c>
-      <c r="G17" s="13">
+      <c r="H17" s="7">
         <v>517679.6499998002</v>
       </c>
-      <c r="H17" s="13">
+      <c r="I17" s="7">
         <v>517692.1599990754</v>
       </c>
-      <c r="I17" s="14">
-        <v>454768.86000001483</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="15" t="s">
+    </row>
+    <row r="18" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="16">
-        <v>371365634.31999928</v>
-      </c>
-      <c r="C18" s="16">
-        <v>326445980.98999941</v>
-      </c>
-      <c r="D18" s="16">
+      <c r="B18" s="9">
+        <v>560257158.49999833</v>
+      </c>
+      <c r="C18" s="9">
+        <v>371356575.50999892</v>
+      </c>
+      <c r="D18" s="9">
+        <v>326276122.17999977</v>
+      </c>
+      <c r="E18" s="9">
         <v>345170525.56999928</v>
       </c>
-      <c r="E18" s="16">
+      <c r="F18" s="9">
         <v>249534748.26999879</v>
       </c>
-      <c r="F18" s="17">
+      <c r="G18" s="10">
         <v>205892753.63999787</v>
       </c>
-      <c r="G18" s="17">
+      <c r="H18" s="10">
         <v>231906909.77999985</v>
       </c>
-      <c r="H18" s="17">
+      <c r="I18" s="10">
         <v>300872924.34999901</v>
       </c>
-      <c r="I18" s="17">
-        <v>282923719.14000028</v>
-      </c>
-      <c r="J18" s="23"/>
-    </row>
-    <row r="19" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="7" t="s">
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="6">
         <v>8000000</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="6">
         <v>8000000</v>
       </c>
-      <c r="D19" s="12">
+      <c r="D19" s="6">
         <v>8000000</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E19" s="6">
         <v>8000000</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="6">
         <v>8000000</v>
       </c>
-      <c r="G19" s="13">
+      <c r="G19" s="7">
         <v>8000000</v>
       </c>
-      <c r="H19" s="13">
+      <c r="H19" s="7">
         <v>8000000</v>
       </c>
-      <c r="I19" s="14">
+      <c r="I19" s="7">
         <v>8000000</v>
       </c>
     </row>
-    <row r="20" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="7" t="s">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="6">
         <v>4000000</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="6">
         <v>4000000</v>
       </c>
-      <c r="D20" s="12">
+      <c r="D20" s="6">
         <v>4000000</v>
       </c>
-      <c r="E20" s="12">
+      <c r="E20" s="6">
         <v>4000000</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20" s="6">
         <v>4000000</v>
       </c>
-      <c r="G20" s="13">
+      <c r="G20" s="7">
         <v>4000000</v>
       </c>
-      <c r="H20" s="13">
+      <c r="H20" s="7">
         <v>4000000</v>
       </c>
-      <c r="I20" s="14">
+      <c r="I20" s="7">
         <v>4000000</v>
       </c>
     </row>
-    <row r="21" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="7" t="s">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="6">
         <v>224248873.15000001</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="6">
         <v>224248873.15000001</v>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="6">
         <v>224248873.15000001</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E21" s="6">
         <v>224248873.15000001</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="6">
         <v>224248873.15000001</v>
       </c>
-      <c r="G21" s="13">
+      <c r="G21" s="7">
         <v>224248873.15000001</v>
       </c>
-      <c r="H21" s="13">
+      <c r="H21" s="7">
         <v>224248873.15000001</v>
       </c>
-      <c r="I21" s="14">
-        <v>205235785.91</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="7" t="s">
+      <c r="I21" s="7">
+        <v>224248873.15000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B22" s="12">
-        <v>43695613.690000013</v>
-      </c>
-      <c r="C22" s="12">
-        <v>44154513.079999991</v>
-      </c>
-      <c r="D22" s="12">
-        <v>41750355.330000013</v>
-      </c>
-      <c r="E22" s="12">
-        <v>31648010.740000036</v>
-      </c>
-      <c r="F22" s="13">
+      <c r="B22" s="6">
+        <v>51004726.350000083</v>
+      </c>
+      <c r="C22" s="6">
+        <v>41496318.080000073</v>
+      </c>
+      <c r="D22" s="6">
+        <v>42121044.420000046</v>
+      </c>
+      <c r="E22" s="6">
+        <v>39544497.830000013</v>
+      </c>
+      <c r="F22" s="6">
+        <v>30726898.240000036</v>
+      </c>
+      <c r="G22" s="7">
         <v>18218555.560000032</v>
       </c>
-      <c r="G22" s="13">
+      <c r="H22" s="7">
         <v>11129867.840000059</v>
       </c>
-      <c r="H22" s="13">
+      <c r="I22" s="7">
         <v>5096691.0900000576</v>
       </c>
-      <c r="I22" s="14">
-        <v>19013087.240000173</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" s="18" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="15" t="s">
+    </row>
+    <row r="23" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="A23" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="16">
-        <v>279944486.84000003</v>
-      </c>
-      <c r="C23" s="16">
-        <v>280403386.23000002</v>
-      </c>
-      <c r="D23" s="16">
-        <v>277999228.48000002</v>
-      </c>
-      <c r="E23" s="16">
-        <v>267896883.89000005</v>
-      </c>
-      <c r="F23" s="17">
+      <c r="B23" s="9">
+        <v>287253599.50000012</v>
+      </c>
+      <c r="C23" s="9">
+        <v>277745191.23000008</v>
+      </c>
+      <c r="D23" s="9">
+        <v>278369917.57000005</v>
+      </c>
+      <c r="E23" s="9">
+        <v>275793370.98000002</v>
+      </c>
+      <c r="F23" s="9">
+        <v>266975771.39000005</v>
+      </c>
+      <c r="G23" s="10">
         <v>254467428.71000004</v>
       </c>
-      <c r="G23" s="17">
+      <c r="H23" s="10">
         <v>247378740.99000007</v>
       </c>
-      <c r="H23" s="17">
+      <c r="I23" s="10">
         <v>241345564.24000007</v>
       </c>
-      <c r="I23" s="17">
-        <v>236248873.15000015</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" s="25" customFormat="1" ht="18.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="24" t="s">
+    </row>
+    <row r="24" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="26">
-        <v>651310121.15999937</v>
-      </c>
-      <c r="C24" s="26">
-        <v>606849367.21999943</v>
-      </c>
-      <c r="D24" s="26">
-        <v>623169754.04999924</v>
-      </c>
-      <c r="E24" s="26">
-        <v>517431632.15999883</v>
-      </c>
-      <c r="F24" s="26">
+      <c r="B24" s="14">
+        <v>847510757.99999845</v>
+      </c>
+      <c r="C24" s="14">
+        <v>649101766.73999906</v>
+      </c>
+      <c r="D24" s="14">
+        <v>604646039.74999976</v>
+      </c>
+      <c r="E24" s="14">
+        <v>620963896.54999924</v>
+      </c>
+      <c r="F24" s="14">
+        <v>516510519.65999883</v>
+      </c>
+      <c r="G24" s="14">
         <v>460360182.34999788</v>
       </c>
-      <c r="G24" s="26">
+      <c r="H24" s="14">
         <v>479285650.76999992</v>
       </c>
-      <c r="H24" s="26">
+      <c r="I24" s="14">
         <v>542218488.58999908</v>
       </c>
-      <c r="I24" s="26">
-        <v>519172592.29000044</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="D27" s="1"/>
-      <c r="E27" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB35" xr:uid="{2387683F-6A26-4967-9F2B-AE7C8F037119}"/>
+  <autoFilter ref="A1:G24" xr:uid="{C4E14BED-4A82-49F0-AB48-4A735E1CAC39}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/5-2026.xlsx
+++ b/5-2026.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\python\balanceSheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F503A8CD-C70D-4849-8D87-686A8909DD4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{26746E4F-A4D2-417F-96ED-BC17B23248EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C7DBF94B-76D0-4DB1-B5F9-1612F1925133}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{FF12AA75-1C76-4EA4-B728-D87BF54824A7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$24</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -197,7 +197,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -219,6 +219,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -273,7 +279,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -308,6 +314,9 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="167" fontId="9" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="9" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -317,7 +326,10 @@
     <xf numFmtId="3" fontId="9" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="6" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -634,73 +646,85 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4E14BED-4A82-49F0-AB48-4A735E1CAC39}">
-  <dimension ref="A1:I24"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{375F69A6-9EFA-4EB5-BE8C-C7AE14F8C1E1}">
+  <dimension ref="A1:K24"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="34.09765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="19.69921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="14.8984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="6" width="20.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="15.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2">
+        <v>46266</v>
+      </c>
+      <c r="C1" s="2">
         <v>46235</v>
       </c>
-      <c r="C1" s="2">
+      <c r="D1" s="2">
         <v>46204</v>
       </c>
-      <c r="D1" s="2">
+      <c r="E1" s="2">
         <v>46174</v>
       </c>
-      <c r="E1" s="2">
+      <c r="F1" s="2">
         <v>46143</v>
       </c>
-      <c r="F1" s="2">
+      <c r="G1" s="2">
         <v>46113</v>
       </c>
-      <c r="G1" s="2">
+      <c r="H1" s="2">
         <v>46082</v>
       </c>
-      <c r="H1" s="2">
+      <c r="I1" s="2">
         <v>46054</v>
       </c>
-      <c r="I1" s="2">
+      <c r="J1" s="2">
         <v>46023</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K1" s="2">
+        <v>45992</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="4">
+        <v>29358304.789999999</v>
+      </c>
+      <c r="C2" s="4">
         <v>29603786.460000001</v>
       </c>
-      <c r="C2" s="4">
+      <c r="D2" s="4">
         <v>23560668.130000003</v>
       </c>
-      <c r="D2" s="4">
+      <c r="E2" s="4">
         <v>22199177.149999999</v>
       </c>
-      <c r="E2" s="4">
+      <c r="F2" s="4">
         <v>21766987.909999996</v>
       </c>
-      <c r="F2" s="4">
+      <c r="G2" s="4">
         <v>21958105.329999998</v>
       </c>
-      <c r="G2" s="5">
+      <c r="H2" s="5">
         <v>19733077.309999999</v>
       </c>
-      <c r="H2" s="5">
+      <c r="I2" s="5">
         <v>19903916.759999998</v>
       </c>
-      <c r="I2" s="5">
+      <c r="J2" s="5">
         <v>20074784.07</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K2" s="16">
+        <v>20245724.849999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -708,28 +732,34 @@
         <v>2394454.15</v>
       </c>
       <c r="C3" s="6">
-        <v>2373214.15</v>
+        <v>2394454.15</v>
       </c>
       <c r="D3" s="6">
         <v>2373214.15</v>
       </c>
       <c r="E3" s="6">
+        <v>2373214.15</v>
+      </c>
+      <c r="F3" s="6">
         <v>2357614.15</v>
       </c>
-      <c r="F3" s="6">
+      <c r="G3" s="6">
         <v>2346114.15</v>
       </c>
-      <c r="G3" s="7">
+      <c r="H3" s="7">
         <v>2232984.15</v>
       </c>
-      <c r="H3" s="7">
+      <c r="I3" s="7">
         <v>2200362.15</v>
       </c>
-      <c r="I3" s="7">
+      <c r="J3" s="7">
         <v>1884602.5</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K3" s="17">
+        <v>1884602.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -748,7 +778,7 @@
       <c r="F4" s="6">
         <v>596741</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="6">
         <v>596741</v>
       </c>
       <c r="H4" s="7">
@@ -757,331 +787,403 @@
       <c r="I4" s="7">
         <v>596741</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="J4" s="7">
+        <v>596741</v>
+      </c>
+      <c r="K4" s="17">
+        <v>596741</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="9">
+        <v>32349499.939999998</v>
+      </c>
+      <c r="C5" s="9">
         <v>32594981.609999999</v>
       </c>
-      <c r="C5" s="9">
+      <c r="D5" s="9">
         <v>26530623.280000001</v>
       </c>
-      <c r="D5" s="9">
+      <c r="E5" s="9">
         <v>25169132.299999997</v>
       </c>
-      <c r="E5" s="9">
+      <c r="F5" s="9">
         <v>24721343.059999995</v>
       </c>
-      <c r="F5" s="9">
+      <c r="G5" s="9">
         <v>24900960.479999997</v>
       </c>
-      <c r="G5" s="10">
+      <c r="H5" s="10">
         <v>22562802.459999997</v>
       </c>
-      <c r="H5" s="10">
+      <c r="I5" s="10">
         <v>22701019.909999996</v>
       </c>
-      <c r="I5" s="10">
+      <c r="J5" s="10">
         <v>22556127.57</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K5" s="10">
+        <v>22727068.349999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="6">
+        <v>321872739.10999995</v>
+      </c>
+      <c r="C6" s="6">
         <v>317508844.450001</v>
       </c>
-      <c r="C6" s="6">
+      <c r="D6" s="6">
         <v>309138879.46999943</v>
       </c>
-      <c r="D6" s="6">
+      <c r="E6" s="6">
         <v>309527001.88999999</v>
       </c>
-      <c r="E6" s="6">
+      <c r="F6" s="6">
         <v>307962482.93999964</v>
       </c>
-      <c r="F6" s="6">
+      <c r="G6" s="6">
         <v>251497026.58999923</v>
       </c>
-      <c r="G6" s="7">
+      <c r="H6" s="7">
         <v>216736145.83000055</v>
       </c>
-      <c r="H6" s="7">
+      <c r="I6" s="7">
         <v>246421191.35999998</v>
       </c>
-      <c r="I6" s="7">
+      <c r="J6" s="7">
         <v>276755395.22999948</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K6" s="17">
+        <v>263703635.98999962</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="6">
-        <v>151212713.38999975</v>
+        <v>202487834.95999914</v>
       </c>
       <c r="C7" s="6">
+        <v>162652062.45999995</v>
+      </c>
+      <c r="D7" s="6">
         <v>67911151.629999876</v>
       </c>
-      <c r="D7" s="6">
+      <c r="E7" s="6">
         <v>57255422.389999941</v>
       </c>
-      <c r="E7" s="6">
+      <c r="F7" s="6">
         <v>51419810.890000179</v>
       </c>
-      <c r="F7" s="6">
+      <c r="G7" s="6">
         <v>34279393.569999754</v>
       </c>
-      <c r="G7" s="7">
+      <c r="H7" s="7">
         <v>36391015.480000034</v>
       </c>
-      <c r="H7" s="7">
+      <c r="I7" s="7">
         <v>35044469.309999794</v>
       </c>
-      <c r="I7" s="7">
+      <c r="J7" s="7">
         <v>40312392.319999546</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K7" s="17">
+        <v>35899338.66000022</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="6">
+        <v>87468184.960000172</v>
+      </c>
+      <c r="C8" s="6">
         <v>61358688.860000148</v>
       </c>
-      <c r="C8" s="6">
+      <c r="D8" s="6">
         <v>51205838.399999842</v>
       </c>
-      <c r="D8" s="6">
+      <c r="E8" s="6">
         <v>59365803.950000517</v>
       </c>
-      <c r="E8" s="6">
+      <c r="F8" s="6">
         <v>88773553.039999709</v>
       </c>
-      <c r="F8" s="6">
+      <c r="G8" s="6">
         <v>80049672.870000184</v>
       </c>
-      <c r="G8" s="7">
+      <c r="H8" s="7">
         <v>69103414.059999168</v>
       </c>
-      <c r="H8" s="7">
+      <c r="I8" s="7">
         <v>62152170.890000343</v>
       </c>
-      <c r="I8" s="7">
+      <c r="J8" s="7">
         <v>73211384.189999923</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K8" s="17">
+        <v>55796550.240000226</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="6">
-        <v>263356694.12</v>
+        <v>257096102.83999991</v>
       </c>
       <c r="C9" s="6">
+        <v>263367858.91999978</v>
+      </c>
+      <c r="D9" s="6">
         <v>172668288.80999997</v>
       </c>
-      <c r="D9" s="6">
+      <c r="E9" s="6">
         <v>149690756.01999947</v>
       </c>
-      <c r="E9" s="6">
+      <c r="F9" s="6">
         <v>144670090.74999979</v>
       </c>
-      <c r="F9" s="6">
+      <c r="G9" s="6">
         <v>122145542.94999963</v>
       </c>
-      <c r="G9" s="7">
+      <c r="H9" s="7">
         <v>111928881.3599996</v>
       </c>
-      <c r="H9" s="7">
+      <c r="I9" s="7">
         <v>109562688.63999996</v>
       </c>
-      <c r="I9" s="7">
+      <c r="J9" s="7">
         <v>125746266.17999986</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K9" s="17">
+        <v>137039113.50999942</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="6">
-        <v>21478836.109999999</v>
+        <v>20621511.82</v>
       </c>
       <c r="C10" s="6">
+        <v>21456177.109999977</v>
+      </c>
+      <c r="D10" s="6">
         <v>21646985.150000002</v>
       </c>
-      <c r="D10" s="6">
+      <c r="E10" s="6">
         <v>3637923.2</v>
       </c>
-      <c r="E10" s="6">
+      <c r="F10" s="6">
         <v>3416615.87</v>
       </c>
-      <c r="F10" s="6">
+      <c r="G10" s="6">
         <v>3637923.2</v>
       </c>
-      <c r="G10" s="7">
+      <c r="H10" s="7">
         <v>3637923.2</v>
       </c>
-      <c r="H10" s="7">
+      <c r="I10" s="7">
         <v>3404110.7</v>
       </c>
-      <c r="I10" s="7">
+      <c r="J10" s="7">
         <v>3636923.24</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="K10" s="17">
+        <v>4006885.54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="9">
-        <v>814915776.9300009</v>
+        <v>889546373.68999922</v>
       </c>
       <c r="C11" s="9">
+        <v>826343631.80000079</v>
+      </c>
+      <c r="D11" s="9">
         <v>622571143.45999908</v>
       </c>
-      <c r="D11" s="9">
+      <c r="E11" s="9">
         <v>579476907.44999993</v>
       </c>
-      <c r="E11" s="9">
+      <c r="F11" s="9">
         <v>596242553.48999929</v>
       </c>
-      <c r="F11" s="9">
+      <c r="G11" s="9">
         <v>491609559.17999882</v>
       </c>
-      <c r="G11" s="10">
+      <c r="H11" s="10">
         <v>437797379.92999935</v>
       </c>
-      <c r="H11" s="10">
+      <c r="I11" s="10">
         <v>456584630.90000004</v>
       </c>
-      <c r="I11" s="10">
+      <c r="J11" s="10">
         <v>519662361.15999877</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="K11" s="10">
+        <v>496445523.93999952</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="15">
-        <v>847510758.54000092</v>
-      </c>
-      <c r="C12" s="15">
+      <c r="B12" s="12">
+        <v>921895873.62999916</v>
+      </c>
+      <c r="C12" s="12">
+        <v>858938613.4100008</v>
+      </c>
+      <c r="D12" s="12">
         <v>649101766.73999906</v>
       </c>
-      <c r="D12" s="15">
+      <c r="E12" s="12">
         <v>604646039.74999988</v>
       </c>
-      <c r="E12" s="15">
+      <c r="F12" s="12">
         <v>620963896.54999924</v>
       </c>
-      <c r="F12" s="12">
+      <c r="G12" s="13">
         <v>516510519.65999883</v>
       </c>
-      <c r="G12" s="12">
+      <c r="H12" s="13">
         <v>460360182.38999933</v>
       </c>
-      <c r="H12" s="12">
+      <c r="I12" s="13">
         <v>479285650.81000006</v>
       </c>
-      <c r="I12" s="12">
+      <c r="J12" s="13">
         <v>542218488.72999883</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K12" s="13">
+        <v>519172592.28999954</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="6">
-        <v>390277405.91999996</v>
+        <v>444160602.1699999</v>
       </c>
       <c r="C13" s="6">
+        <v>400932227.10999995</v>
+      </c>
+      <c r="D13" s="6">
         <v>253155600.78000042</v>
       </c>
-      <c r="D13" s="6">
+      <c r="E13" s="6">
         <v>216556629.12999955</v>
       </c>
-      <c r="E13" s="6">
+      <c r="F13" s="6">
         <v>221490803.47</v>
       </c>
-      <c r="F13" s="6">
+      <c r="G13" s="6">
         <v>120354247.44999973</v>
       </c>
-      <c r="G13" s="7">
+      <c r="H13" s="7">
         <v>105458756.66999979</v>
       </c>
-      <c r="H13" s="7">
+      <c r="I13" s="7">
         <v>133665877.53000003</v>
       </c>
-      <c r="I13" s="7">
+      <c r="J13" s="7">
         <v>177227503.53999999</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K13" s="17">
+        <v>148043033.26000029</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B14" s="6">
-        <v>14045413.12999998</v>
+        <v>20505879.709999979</v>
       </c>
       <c r="C14" s="6">
+        <v>14772004.119999956</v>
+      </c>
+      <c r="D14" s="6">
         <v>15241394.300000006</v>
       </c>
-      <c r="D14" s="6">
+      <c r="E14" s="6">
         <v>12216539.409999972</v>
       </c>
-      <c r="E14" s="6">
+      <c r="F14" s="6">
         <v>17960661.13000001</v>
       </c>
-      <c r="F14" s="6">
+      <c r="G14" s="6">
         <v>24891599.720000021</v>
       </c>
-      <c r="G14" s="7">
+      <c r="H14" s="7">
         <v>21895473.599999938</v>
       </c>
-      <c r="H14" s="7">
+      <c r="I14" s="7">
         <v>24608773.970000006</v>
       </c>
-      <c r="I14" s="7">
+      <c r="J14" s="7">
         <v>28574676.589999989</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K14" s="17">
+        <v>26189842.269999973</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B15" s="6">
+        <v>164170988.31</v>
+      </c>
+      <c r="C15" s="6">
         <v>154629693.79000002</v>
       </c>
-      <c r="C15" s="6">
+      <c r="D15" s="6">
         <v>101654934.77000012</v>
       </c>
-      <c r="D15" s="6">
+      <c r="E15" s="6">
         <v>96198307.679999903</v>
       </c>
-      <c r="E15" s="6">
+      <c r="F15" s="6">
         <v>104414415.23000011</v>
       </c>
-      <c r="F15" s="6">
+      <c r="G15" s="6">
         <v>102984255.44000015</v>
       </c>
-      <c r="G15" s="7">
+      <c r="H15" s="7">
         <v>77233877.720000073</v>
       </c>
-      <c r="H15" s="7">
+      <c r="I15" s="7">
         <v>72327612.63000001</v>
       </c>
-      <c r="I15" s="7">
+      <c r="J15" s="7">
         <v>93766086.059999973</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K15" s="17">
+        <v>107449108.75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="6">
         <v>786966</v>
       </c>
       <c r="C16" s="7">
@@ -1105,66 +1207,84 @@
       <c r="I16" s="7">
         <v>786966</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J16" s="7">
+        <v>786966</v>
+      </c>
+      <c r="K16" s="17">
+        <v>786966</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B17" s="6">
+        <v>517679.89999908494</v>
+      </c>
+      <c r="C17" s="6">
+        <v>517679.40000063466</v>
+      </c>
+      <c r="D17" s="6">
         <v>517679.65999836015</v>
       </c>
-      <c r="C17" s="6">
-        <v>517679.65999836015</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="E17" s="6">
         <v>517679.96000033902</v>
       </c>
-      <c r="E17" s="6">
+      <c r="F17" s="6">
         <v>517679.73999911832</v>
       </c>
-      <c r="F17" s="6">
+      <c r="G17" s="6">
         <v>517679.65999889659</v>
       </c>
-      <c r="G17" s="7">
+      <c r="H17" s="7">
         <v>517679.64999807166</v>
       </c>
-      <c r="H17" s="7">
+      <c r="I17" s="7">
         <v>517679.6499998002</v>
       </c>
-      <c r="I17" s="7">
+      <c r="J17" s="7">
         <v>517692.1599990754</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="K17" s="17">
+        <v>454768.86000001483</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
         <v>15</v>
       </c>
       <c r="B18" s="9">
-        <v>560257158.49999833</v>
+        <v>630142116.08999896</v>
       </c>
       <c r="C18" s="9">
+        <v>571638570.42000067</v>
+      </c>
+      <c r="D18" s="9">
         <v>371356575.50999892</v>
       </c>
-      <c r="D18" s="9">
+      <c r="E18" s="9">
         <v>326276122.17999977</v>
       </c>
-      <c r="E18" s="9">
+      <c r="F18" s="9">
         <v>345170525.56999928</v>
       </c>
-      <c r="F18" s="9">
+      <c r="G18" s="9">
         <v>249534748.26999879</v>
       </c>
-      <c r="G18" s="10">
+      <c r="H18" s="10">
         <v>205892753.63999787</v>
       </c>
-      <c r="H18" s="10">
+      <c r="I18" s="10">
         <v>231906909.77999985</v>
       </c>
-      <c r="I18" s="10">
+      <c r="J18" s="10">
         <v>300872924.34999901</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K18" s="10">
+        <v>282923719.14000028</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>16</v>
       </c>
@@ -1183,7 +1303,7 @@
       <c r="F19" s="6">
         <v>8000000</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G19" s="6">
         <v>8000000</v>
       </c>
       <c r="H19" s="7">
@@ -1192,8 +1312,14 @@
       <c r="I19" s="7">
         <v>8000000</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J19" s="7">
+        <v>8000000</v>
+      </c>
+      <c r="K19" s="17">
+        <v>8000000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>17</v>
       </c>
@@ -1212,7 +1338,7 @@
       <c r="F20" s="6">
         <v>4000000</v>
       </c>
-      <c r="G20" s="7">
+      <c r="G20" s="6">
         <v>4000000</v>
       </c>
       <c r="H20" s="7">
@@ -1221,8 +1347,14 @@
       <c r="I20" s="7">
         <v>4000000</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J20" s="7">
+        <v>4000000</v>
+      </c>
+      <c r="K20" s="17">
+        <v>4000000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>18</v>
       </c>
@@ -1241,7 +1373,7 @@
       <c r="F21" s="6">
         <v>224248873.15000001</v>
       </c>
-      <c r="G21" s="7">
+      <c r="G21" s="6">
         <v>224248873.15000001</v>
       </c>
       <c r="H21" s="7">
@@ -1250,96 +1382,120 @@
       <c r="I21" s="7">
         <v>224248873.15000001</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J21" s="7">
+        <v>224248873.15000001</v>
+      </c>
+      <c r="K21" s="17">
+        <v>205235785.91</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B22" s="6">
-        <v>51004726.350000083</v>
+        <v>55504884.390000105</v>
       </c>
       <c r="C22" s="6">
+        <v>51051169.840000093</v>
+      </c>
+      <c r="D22" s="6">
         <v>41496318.080000073</v>
       </c>
-      <c r="D22" s="6">
+      <c r="E22" s="6">
         <v>42121044.420000046</v>
       </c>
-      <c r="E22" s="6">
+      <c r="F22" s="6">
         <v>39544497.830000013</v>
       </c>
-      <c r="F22" s="6">
+      <c r="G22" s="6">
         <v>30726898.240000036</v>
       </c>
-      <c r="G22" s="7">
+      <c r="H22" s="7">
         <v>18218555.560000032</v>
       </c>
-      <c r="H22" s="7">
+      <c r="I22" s="7">
         <v>11129867.840000059</v>
       </c>
-      <c r="I22" s="7">
+      <c r="J22" s="7">
         <v>5096691.0900000576</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
+      <c r="K22" s="17">
+        <v>19013087.240000173</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B23" s="9">
-        <v>287253599.50000012</v>
+        <v>291753757.54000008</v>
       </c>
       <c r="C23" s="9">
+        <v>287300042.99000013</v>
+      </c>
+      <c r="D23" s="9">
         <v>277745191.23000008</v>
       </c>
-      <c r="D23" s="9">
+      <c r="E23" s="9">
         <v>278369917.57000005</v>
       </c>
-      <c r="E23" s="9">
+      <c r="F23" s="9">
         <v>275793370.98000002</v>
       </c>
-      <c r="F23" s="9">
+      <c r="G23" s="9">
         <v>266975771.39000005</v>
       </c>
-      <c r="G23" s="10">
+      <c r="H23" s="10">
         <v>254467428.71000004</v>
       </c>
-      <c r="H23" s="10">
+      <c r="I23" s="10">
         <v>247378740.99000007</v>
       </c>
-      <c r="I23" s="10">
+      <c r="J23" s="10">
         <v>241345564.24000007</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="13" t="s">
+      <c r="K23" s="10">
+        <v>236248873.15000015</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="18.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="14">
-        <v>847510757.99999845</v>
-      </c>
-      <c r="C24" s="14">
+      <c r="B24" s="15">
+        <v>921895873.62999904</v>
+      </c>
+      <c r="C24" s="15">
+        <v>858938613.4100008</v>
+      </c>
+      <c r="D24" s="15">
         <v>649101766.73999906</v>
       </c>
-      <c r="D24" s="14">
+      <c r="E24" s="15">
         <v>604646039.74999976</v>
       </c>
-      <c r="E24" s="14">
+      <c r="F24" s="15">
         <v>620963896.54999924</v>
       </c>
-      <c r="F24" s="14">
+      <c r="G24" s="15">
         <v>516510519.65999883</v>
       </c>
-      <c r="G24" s="14">
+      <c r="H24" s="15">
         <v>460360182.34999788</v>
       </c>
-      <c r="H24" s="14">
+      <c r="I24" s="15">
         <v>479285650.76999992</v>
       </c>
-      <c r="I24" s="14">
+      <c r="J24" s="15">
         <v>542218488.58999908</v>
       </c>
+      <c r="K24" s="15">
+        <v>519172592.29000044</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G24" xr:uid="{C4E14BED-4A82-49F0-AB48-4A735E1CAC39}"/>
+  <autoFilter ref="A1:K24" xr:uid="{375F69A6-9EFA-4EB5-BE8C-C7AE14F8C1E1}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>